--- a/filer/14996613_valse.xlsx
+++ b/filer/14996613_valse.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/14996613_valse.xlsx
+++ b/filer/14996613_valse.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_14996613" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_14996613" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_14996613" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_14996613" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2817,35 +2818,35 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
@@ -4199,19 +4200,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
@@ -4317,19 +4318,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4626,6 +4627,148 @@
       </c>
       <c r="F95" s="13">
         <f>IFERROR($F$32/($F$57+$F$64)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_14996613'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_14996613'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_14996613'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_14996613'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_14996613'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_14996613'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_14996613'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_14996613'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_14996613'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_14996613'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_14996613'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_14996613'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_14996613'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_14996613'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_14996613'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_14996613'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_14996613'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_14996613'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_14996613'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_14996613'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B102">
+        <f>IF(ABS(('pengestrom_raw_14996613'!$B$2+'pengestrom_raw_14996613'!$B$3+'pengestrom_raw_14996613'!$B$4)-'pengestrom_raw_14996613'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_14996613'!$B$2+'pengestrom_raw_14996613'!$B$3+'pengestrom_raw_14996613'!$B$4)-'pengestrom_raw_14996613'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C102">
+        <f>IF(ABS(('pengestrom_raw_14996613'!$C$2+'pengestrom_raw_14996613'!$C$3+'pengestrom_raw_14996613'!$C$4)-'pengestrom_raw_14996613'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_14996613'!$C$2+'pengestrom_raw_14996613'!$C$3+'pengestrom_raw_14996613'!$C$4)-'pengestrom_raw_14996613'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D102">
+        <f>IF(ABS(('pengestrom_raw_14996613'!$D$2+'pengestrom_raw_14996613'!$D$3+'pengestrom_raw_14996613'!$D$4)-'pengestrom_raw_14996613'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_14996613'!$D$2+'pengestrom_raw_14996613'!$D$3+'pengestrom_raw_14996613'!$D$4)-'pengestrom_raw_14996613'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E102">
+        <f>IF(ABS(('pengestrom_raw_14996613'!$E$2+'pengestrom_raw_14996613'!$E$3+'pengestrom_raw_14996613'!$E$4)-'pengestrom_raw_14996613'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_14996613'!$E$2+'pengestrom_raw_14996613'!$E$3+'pengestrom_raw_14996613'!$E$4)-'pengestrom_raw_14996613'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F102">
+        <f>IF(ABS(('pengestrom_raw_14996613'!$F$2+'pengestrom_raw_14996613'!$F$3+'pengestrom_raw_14996613'!$F$4)-'pengestrom_raw_14996613'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_14996613'!$F$2+'pengestrom_raw_14996613'!$F$3+'pengestrom_raw_14996613'!$F$4)-'pengestrom_raw_14996613'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4658,412 +4801,412 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>611643</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>658835</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>778921</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>880300</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>806421</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>850775</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>643</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>650</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>6879</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>7016</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>7945</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>10060</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>439301</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>477884</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>600809</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>667228</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>601515</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>637037</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>50624</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>49109</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>56119</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>65306</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>72529</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>73013</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>122361</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>132492</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>128872</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>154782</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>140322</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>150785</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>67646</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>70849</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>78338</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>86959</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>88183</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>95507</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>15370</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>16811</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>16585</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>17564</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>18529</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>21204</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>39345</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>44832</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>33949</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>50259</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>33610</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>33074</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>404</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>438</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>476</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>69</v>
       </c>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
+        <v>231</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>386</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>1701</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>756</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Finansielle omkostninger</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>1462</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>2896</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>6835</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle poster, netto</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>634</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>1086</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>4860</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>-6591</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Resultat før skat</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>44198</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>32863</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>49149</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>28750</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>26483</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Skat af årets resultat</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>9669</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>7172</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>10780</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>6076</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>6126</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Årets resultat</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>34529</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>25691</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>38369</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>22674</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>20357</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="F19" s="17" t="n">
         <v>142</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>231</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>386</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>1701</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Finansielle omkostninger</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1496</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>1462</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>1948</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>2896</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>5685</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle poster, netto</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>833</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>634</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>1086</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>4860</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Resultat før skat</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>38512</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>44198</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>32863</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>49149</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>28750</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Skat af årets resultat</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>8418</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>9669</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>7172</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>10780</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>6076</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Årets resultat</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>30094</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>34529</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>25691</v>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>38369</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>22674</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Gns. antal medarbejdere</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>129</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>133</v>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>134</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>136</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>30030</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>19996</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>26857</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>26416</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>30677</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>65610</v>
       </c>
     </row>
   </sheetData>
@@ -5095,1041 +5238,1043 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>63263</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>68293</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>65702</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>86478</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>89485</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>108998</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>108397</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>109298</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>108169</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>107935</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>109732</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>110832</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n">
+        <v>1356</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n"/>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>12534</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>9788</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>23780</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>12089</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>19209</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>65369</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>184194</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>187379</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>197651</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>206502</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>218426</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>286555</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>1670</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>2108</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>2584</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>2669</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>2738</v>
       </c>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>568</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>580</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>580</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>586</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>791</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>319</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>2238</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>2688</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>3164</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>3255</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>3529</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>319</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>186432</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>190067</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>200815</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>209757</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>221955</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>286874</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>55534</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>59500</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>83406</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>66026</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>95300</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>55636</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>19967</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>18311</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>26012</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>28206</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>27027</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>30410</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>75501</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>77811</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>109418</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>94232</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>122327</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>86046</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>57614</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>65005</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>118095</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>99994</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>83719</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>84504</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>2160</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>3095</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>17753</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>3714</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>24134</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>3234</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>2324</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>2029</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1076</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>2751</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>880</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>640</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>1386</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>1990</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>2035</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>950</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>2128</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>70034</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>76100</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>139972</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>106819</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>111554</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>90746</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>816</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>6056</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>1140</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>7148</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>417</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>12126</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>146351</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>159967</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>250530</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>208199</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>234298</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>188918</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>332783</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>350034</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>451345</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>417956</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>456253</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>475792</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>5000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>-1762</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>-1037</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>-240</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>1013</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>2702</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>-2784</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>147148</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>161677</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>168421</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>185790</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>179464</v>
       </c>
+      <c r="F33" s="17" t="n">
+        <v>186821</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>162386</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>185640</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>192128</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>212803</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>216166</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>202037</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>12173</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>13442</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>14189</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>14553</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>15305</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>17340</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>12173</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>13442</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>14189</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>14553</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>15305</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>17340</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>36010</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>34011</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>44389</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>42081</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>50908</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>54355</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>11579</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>10609</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>9660</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>8702</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>7670</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>42731</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>49370</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>57799</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>53533</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>69093</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>109024</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>3972</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>4332</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>4422</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>5160</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>8835</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>10247</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>82683</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>22610</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>64344</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>35473</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>50871</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>61170</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>58253</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>52445</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>65356</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n">
+        <v>4645</v>
+      </c>
+      <c r="E47" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
-        <v>53339</v>
-      </c>
-      <c r="C41" s="16" t="n">
-        <v>49370</v>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>57799</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>53533</v>
-      </c>
-      <c r="F41" s="16" t="n">
-        <v>69093</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>3944</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>3972</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>4332</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>4422</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>5160</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>12689</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>10247</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>82683</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>22610</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>64344</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n">
-        <v>42270</v>
-      </c>
-      <c r="C46" s="16" t="n">
-        <v>50871</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>61170</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>58253</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>52445</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n">
-        <v>4645</v>
-      </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>7026</v>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>8603</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>6853</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>10770</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>27889</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>31523</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>35699</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>27399</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>33802</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n">
+        <v>668</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>668</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>541</v>
+      </c>
+      <c r="F52" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n">
-        <v>8603</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>6853</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>10770</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>5800</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>38956</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>27889</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>31523</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>35699</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>27399</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n">
-        <v>668</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>668</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>541</v>
-      </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>104885</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>101582</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>187229</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>137067</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>155689</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>147391</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>158224</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>150952</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>245028</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>190600</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>224782</v>
       </c>
+      <c r="F54" s="17" t="n">
+        <v>256415</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>332783</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>350034</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>451345</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>417956</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>456253</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>475792</v>
       </c>
     </row>
   </sheetData>
@@ -6138,6 +6283,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>50430</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-30895</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>122480</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>-2161</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>110364</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-20008</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-26846</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-26422</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-30834</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-65468</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-15942</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>61225</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-83197</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>37034</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-27682</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6168,13 +6435,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6888,7 +7155,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7006,7 +7273,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7182,7 +7449,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7360,7 +7627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7405,27 +7672,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7450,10 +7717,10 @@
           <t>fsa:AdjustmentsForDeferredTaxCashFlow</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n"/>
-      <c r="E3" s="35" t="n">
+      <c r="D3" s="35" t="n">
         <v>928</v>
       </c>
+      <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
@@ -7479,10 +7746,10 @@
           <t>fsa:AdjustmentsOfDividendsFromParticipatingInterests</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n">
+      <c r="D4" s="38" t="n">
         <v>1462</v>
       </c>
+      <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
       <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n"/>
@@ -7508,10 +7775,10 @@
           <t>fsa:AdjustmentsOfProfitLossFromParticipatingInterestsAfterTax</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n">
+      <c r="D5" s="35" t="n">
         <v>-390</v>
       </c>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n"/>
@@ -7537,10 +7804,10 @@
           <t>fsa:AdjustmentsOfShareBasedPayment</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n">
+      <c r="D6" s="38" t="n">
         <v>9669</v>
       </c>
+      <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n"/>
@@ -7567,17 +7834,15 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>7296</v>
+        <v>6608</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>6608</v>
+        <v>105</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>105</v>
-      </c>
-      <c r="G7" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="35" t="n"/>
       <c r="H7" s="35" t="n"/>
       <c r="I7" s="36" t="inlineStr">
         <is>
